--- a/data/output/2025/evaluasi_18.xlsx
+++ b/data/output/2025/evaluasi_18.xlsx
@@ -1298,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,6 +1442,90 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Metro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Metro</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.355759058518927</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Metro</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8439313462207448</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1600,6 +1684,174 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.076862345027124</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.131989897663627</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>29.40359109594308</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.287500200934374</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3029824086109598</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,6 +2038,146 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanggamus</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.344536074258711</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1802</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanggamus</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>31.3340341830801</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1802</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanggamus</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1802</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanggamus</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.350966004113051</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1802</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanggamus</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2524367595804006</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1800,7 +2192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1860,6 +2252,230 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.976005452137962</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.539520577012766</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>30.46365529710701</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5716664179232783</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3235395129003437</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.9143293989598764</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.940624997913528</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1874,7 +2490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2074,6 +2690,90 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pesawaran</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Pesawaran</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>18.55692087373689</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Pesawaran</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>18.81675786626827</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2218,18 +2918,74 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>35.07442457579999</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1810</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pringsewu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1810</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pringsewu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>-2.417174421388096</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2246,7 +3002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2292,18 +3048,214 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>-0.7017805100174569</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1871</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.028315865861847</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1871</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1871</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.02906920871651065</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1871</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.481221331048144</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1871</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.72390896935585</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1871</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.02779706369126608</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1871</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>-2.561129442253469</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2320,7 +3272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2520,6 +3472,174 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.213793788461027</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>32.31458084327053</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.142351533763134</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2045277736350241</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.978913518990146</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2534,7 +3654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2734,6 +3854,202 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.345206889610949</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>30.94029634402133</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.508834653576374</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1810219597319599</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.263424847697316</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.359325719251184</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2748,7 +4064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2948,6 +4264,62 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Way Kanan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>32.96356723211979</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Way Kanan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2962,7 +4334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +4450,118 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mesuji</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>44.92111727543281</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Mesuji</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mesuji</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.94469854660989</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mesuji</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.877513274712832</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3092,7 +4576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3278,18 +4762,74 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1812</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulang Bawang Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.7446519834816375</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1812</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulang Bawang Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>-3.28409534955376</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3306,7 +4846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3366,6 +4906,62 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1813</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pesisir Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1813</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pesisir Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.737509273201686</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3380,7 +4976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3468,6 +5064,230 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulang Bawang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>50.389496890537</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulang Bawang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulang Bawang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.317841858143872</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulang Bawang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.411371485690807</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulang Bawang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.6619046104519353</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulang Bawang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.4508453384892004</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulang Bawang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.111418132694635</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulang Bawang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.063834556208903</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3482,7 +5302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3629,6 +5449,174 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.159113835369869</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>33.81723998173198</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.009869647528872</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4788952120508861</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.088371771111373</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
